--- a/data/dividends_info_20260603.xlsx
+++ b/data/dividends_info_20260603.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>68.87000274658203</v>
+        <v>68.48999786376953</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1306809879639022</v>
+        <v>0.1314060487766624</v>
       </c>
       <c r="J2" t="n">
         <v>285</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>54.70000076293945</v>
+        <v>55</v>
       </c>
       <c r="I3" t="n">
-        <v>1.279707477580634</v>
+        <v>1.272727272727272</v>
       </c>
       <c r="J3" t="n">
         <v>264</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.020000457763672</v>
+        <v>9.079999923706055</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6651884363083036</v>
+        <v>0.6607929570941081</v>
       </c>
       <c r="J4" t="n">
         <v>194</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>68.87000274658203</v>
+        <v>68.48999786376953</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1306809879639022</v>
+        <v>0.1314060487766624</v>
       </c>
       <c r="J6" t="n">
         <v>194</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.109999895095825</v>
+        <v>2.075000047683716</v>
       </c>
       <c r="I7" t="n">
-        <v>3.649289280960038</v>
+        <v>3.710843288218411</v>
       </c>
       <c r="J7" t="n">
         <v>173</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.39999961853027</v>
+        <v>23.45499992370605</v>
       </c>
       <c r="I8" t="n">
-        <v>1.153846172656299</v>
+        <v>1.151140485518015</v>
       </c>
       <c r="J8" t="n">
         <v>173</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.550000190734863</v>
+        <v>5.510000228881836</v>
       </c>
       <c r="I9" t="n">
-        <v>3.603603479759853</v>
+        <v>3.629763914557708</v>
       </c>
       <c r="J9" t="n">
         <v>166</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.96999979019165</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J13" t="n">
         <v>117</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.40999984741211</v>
+        <v>23.45499992370605</v>
       </c>
       <c r="I14" t="n">
-        <v>1.15335327535189</v>
+        <v>1.151140485518015</v>
       </c>
       <c r="J14" t="n">
         <v>110</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>68.87000274658203</v>
+        <v>68.48999786376953</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1306809879639022</v>
+        <v>0.1314060487766624</v>
       </c>
       <c r="J15" t="n">
         <v>110</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.900000095367432</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I16" t="n">
-        <v>5.08474568052218</v>
+        <v>5.119453808272897</v>
       </c>
       <c r="J16" t="n">
         <v>103</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.96999979019165</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J18" t="n">
         <v>61</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.960000038146973</v>
+        <v>6.03000020980835</v>
       </c>
       <c r="I19" t="n">
-        <v>4.194630845635492</v>
+        <v>4.145936837503786</v>
       </c>
       <c r="J19" t="n">
         <v>54</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.489999771118164</v>
+        <v>4.460000038146973</v>
       </c>
       <c r="I20" t="n">
-        <v>3.118040248031799</v>
+        <v>3.1390134260664</v>
       </c>
       <c r="J20" t="n">
         <v>47</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.529999732971191</v>
+        <v>9.479999542236328</v>
       </c>
       <c r="I21" t="n">
-        <v>2.728226729120161</v>
+        <v>2.742616166188824</v>
       </c>
       <c r="J21" t="n">
         <v>47</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.88000011444092</v>
+        <v>14.85999965667725</v>
       </c>
       <c r="I22" t="n">
-        <v>4.032258033504347</v>
+        <v>4.037685153851224</v>
       </c>
       <c r="J22" t="n">
         <v>47</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.644000053405762</v>
+        <v>3.611999988555908</v>
       </c>
       <c r="I23" t="n">
-        <v>6.037321536106544</v>
+        <v>6.090808435687644</v>
       </c>
       <c r="J23" t="n">
         <v>47</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.204999923706055</v>
+        <v>6.135000228881836</v>
       </c>
       <c r="I25" t="n">
-        <v>1.611603565343367</v>
+        <v>1.629991789229745</v>
       </c>
       <c r="J25" t="n">
         <v>47</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I26" t="n">
-        <v>1.978947368421053</v>
+        <v>2.000000081163775</v>
       </c>
       <c r="J26" t="n">
         <v>47</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.820000171661377</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I27" t="n">
-        <v>2.061855609288493</v>
+        <v>2.058319066387184</v>
       </c>
       <c r="J27" t="n">
         <v>40</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.320000171661377</v>
+        <v>4.369999885559082</v>
       </c>
       <c r="I31" t="n">
-        <v>1.620370305982639</v>
+        <v>1.601830705564068</v>
       </c>
       <c r="J31" t="n">
         <v>33</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>33.5</v>
+        <v>33.75</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4477611940298508</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="J32" t="n">
         <v>33</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.75</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6896551497342619</v>
       </c>
       <c r="J33" t="n">
         <v>26</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.36000061035156</v>
+        <v>22.31999969482422</v>
       </c>
       <c r="I34" t="n">
-        <v>4.248658202451915</v>
+        <v>4.256272459628641</v>
       </c>
       <c r="J34" t="n">
         <v>19</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>32</v>
+        <v>31.79999923706055</v>
       </c>
       <c r="I35" t="n">
-        <v>0.609375</v>
+        <v>0.6132075618817686</v>
       </c>
       <c r="J35" t="n">
         <v>19</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.865000009536743</v>
+        <v>1.850000023841858</v>
       </c>
       <c r="I36" t="n">
-        <v>1.769436988270957</v>
+        <v>1.783783760795287</v>
       </c>
       <c r="J36" t="n">
         <v>19</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.752000093460083</v>
+        <v>3.73799991607666</v>
       </c>
       <c r="I38" t="n">
-        <v>4.264392217870349</v>
+        <v>4.280363927025799</v>
       </c>
       <c r="J38" t="n">
         <v>19</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.608000040054321</v>
+        <v>2.589999914169312</v>
       </c>
       <c r="I39" t="n">
-        <v>5.314417096293953</v>
+        <v>5.351351528691191</v>
       </c>
       <c r="J39" t="n">
         <v>19</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>51.09999847412109</v>
+        <v>50.86999893188477</v>
       </c>
       <c r="I40" t="n">
-        <v>1.232876749143261</v>
+        <v>1.238450979414357</v>
       </c>
       <c r="J40" t="n">
         <v>19</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5.965000152587891</v>
+        <v>5.985000133514404</v>
       </c>
       <c r="I41" t="n">
-        <v>2.347024248427916</v>
+        <v>2.339181234366853</v>
       </c>
       <c r="J41" t="n">
         <v>19</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>19.45000076293945</v>
+        <v>19.20000076293945</v>
       </c>
       <c r="I42" t="n">
-        <v>4.010282619043556</v>
+        <v>4.06249983857076</v>
       </c>
       <c r="J42" t="n">
         <v>19</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>25.70999908447266</v>
+        <v>25.47999954223633</v>
       </c>
       <c r="I43" t="n">
-        <v>3.306106691047494</v>
+        <v>3.335949824453557</v>
       </c>
       <c r="J43" t="n">
         <v>19</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>68.87000274658203</v>
+        <v>68.48999786376953</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1306809879639022</v>
+        <v>0.1314060487766624</v>
       </c>
       <c r="J44" t="n">
         <v>19</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.450000047683716</v>
+        <v>1.409999966621399</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6896551497342619</v>
+        <v>0.709219874945225</v>
       </c>
       <c r="J45" t="n">
         <v>19</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.199999809265137</v>
+        <v>6.223999977111816</v>
       </c>
       <c r="I46" t="n">
-        <v>2.924193638346076</v>
+        <v>2.912917748501188</v>
       </c>
       <c r="J46" t="n">
         <v>19</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.890000343322754</v>
+        <v>8.739999771118164</v>
       </c>
       <c r="I47" t="n">
-        <v>2.924634307751012</v>
+        <v>2.974828453190412</v>
       </c>
       <c r="J47" t="n">
         <v>19</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.781999588012695</v>
+        <v>9.826000213623047</v>
       </c>
       <c r="I48" t="n">
-        <v>2.831731871461622</v>
+        <v>2.819051434743094</v>
       </c>
       <c r="J48" t="n">
         <v>19</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.002000093460083</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="I50" t="n">
-        <v>3.664223736689323</v>
+        <v>3.63036307058268</v>
       </c>
       <c r="J50" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.160000085830688</v>
+        <v>3.200000047683716</v>
       </c>
       <c r="I52" t="n">
-        <v>5.063291001713369</v>
+        <v>4.999999925494195</v>
       </c>
       <c r="J52" t="n">
         <v>5</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.9049999713897705</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="I53" t="n">
-        <v>2.762431026556669</v>
+        <v>2.747252668077397</v>
       </c>
       <c r="J53" t="n">
         <v>5</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.85000038146973</v>
+        <v>27.75</v>
       </c>
       <c r="I54" t="n">
-        <v>3.985637288315981</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>1</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4979999959468842</v>
+        <v>0.4855000078678131</v>
       </c>
       <c r="I56" t="n">
-        <v>4.618473933171105</v>
+        <v>4.737384063289697</v>
       </c>
       <c r="J56" t="n">
         <v>-2</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>19.95000076293945</v>
+        <v>19.89999961853027</v>
       </c>
       <c r="I57" t="n">
-        <v>3.00751868197721</v>
+        <v>3.015075434681407</v>
       </c>
       <c r="J57" t="n">
         <v>-2</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.279999732971191</v>
+        <v>9.319999694824219</v>
       </c>
       <c r="I58" t="n">
-        <v>2.15517247580745</v>
+        <v>2.145922817047604</v>
       </c>
       <c r="J58" t="n">
         <v>-2</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.315000057220459</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="I59" t="n">
-        <v>7.775377777576378</v>
+        <v>7.894736941171156</v>
       </c>
       <c r="J59" t="n">
         <v>-9</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>16</v>
+        <v>15.93000030517578</v>
       </c>
       <c r="I61" t="n">
-        <v>1.5625</v>
+        <v>1.569365946080824</v>
       </c>
       <c r="J61" t="n">
         <v>-9</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.799999952316284</v>
+        <v>3.839999914169312</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7894736941171157</v>
+        <v>0.7812500174622986</v>
       </c>
       <c r="J62" t="n">
         <v>-9</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.099999904632568</v>
+        <v>4.130000114440918</v>
       </c>
       <c r="I63" t="n">
-        <v>3.658536670464694</v>
+        <v>3.631961158439475</v>
       </c>
       <c r="J63" t="n">
         <v>-9</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.64999961853027</v>
+        <v>12.69999980926514</v>
       </c>
       <c r="I64" t="n">
-        <v>4.584980375417487</v>
+        <v>4.566929202446662</v>
       </c>
       <c r="J64" t="n">
         <v>-9</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.214999914169312</v>
+        <v>2.20199990272522</v>
       </c>
       <c r="I65" t="n">
-        <v>4.695259775619584</v>
+        <v>4.722979318540769</v>
       </c>
       <c r="J65" t="n">
         <v>-16</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10.80500030517578</v>
+        <v>10.58500003814697</v>
       </c>
       <c r="I66" t="n">
-        <v>2.683942543352682</v>
+        <v>2.739726017523641</v>
       </c>
       <c r="J66" t="n">
         <v>-16</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.109999895095825</v>
+        <v>2.075000047683716</v>
       </c>
       <c r="I67" t="n">
-        <v>3.649289280960038</v>
+        <v>3.710843288218411</v>
       </c>
       <c r="J67" t="n">
         <v>-16</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>38.90000152587891</v>
+        <v>38.84999847412109</v>
       </c>
       <c r="I68" t="n">
-        <v>4.215938137968866</v>
+        <v>4.221364387163215</v>
       </c>
       <c r="J68" t="n">
         <v>-16</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>34.2599983215332</v>
+        <v>34.06999969482422</v>
       </c>
       <c r="I69" t="n">
-        <v>5.837711903047449</v>
+        <v>5.870267149734762</v>
       </c>
       <c r="J69" t="n">
         <v>-16</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.303999900817871</v>
+        <v>3.302000045776367</v>
       </c>
       <c r="I70" t="n">
-        <v>3.026634473422534</v>
+        <v>3.028467553412404</v>
       </c>
       <c r="J70" t="n">
         <v>-16</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>37.68000030517578</v>
+        <v>37.43000030517578</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3940021199511702</v>
+        <v>0.3966337130365215</v>
       </c>
       <c r="J71" t="n">
         <v>-16</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>19.95999908447266</v>
+        <v>19.69000053405762</v>
       </c>
       <c r="I72" t="n">
-        <v>4.609218648289866</v>
+        <v>4.672422422786044</v>
       </c>
       <c r="J72" t="n">
         <v>-16</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.93000030517578</v>
+        <v>11.77999973297119</v>
       </c>
       <c r="I73" t="n">
-        <v>2.514668837601339</v>
+        <v>2.546689361633228</v>
       </c>
       <c r="J73" t="n">
         <v>-16</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>82.5</v>
+        <v>81.05999755859375</v>
       </c>
       <c r="I74" t="n">
-        <v>1.260606060606061</v>
+        <v>1.283000285372871</v>
       </c>
       <c r="J74" t="n">
         <v>-16</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>43.84999847412109</v>
+        <v>43.81000137329102</v>
       </c>
       <c r="I75" t="n">
-        <v>1.596351252812741</v>
+        <v>1.5978086693847</v>
       </c>
       <c r="J75" t="n">
         <v>-16</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>54.70000076293945</v>
+        <v>55</v>
       </c>
       <c r="I76" t="n">
-        <v>4.021937786681993</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>-16</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>8.928999900817871</v>
+        <v>8.895000457763672</v>
       </c>
       <c r="I77" t="n">
-        <v>9.631537793176886</v>
+        <v>9.668352509744739</v>
       </c>
       <c r="J77" t="n">
         <v>-16</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>11.5959997177124</v>
+        <v>11.49199962615967</v>
       </c>
       <c r="I78" t="n">
-        <v>4.829251583583807</v>
+        <v>4.872955257719041</v>
       </c>
       <c r="J78" t="n">
         <v>-16</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2.170000076293945</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I79" t="n">
-        <v>1.843317907541938</v>
+        <v>1.834862329132901</v>
       </c>
       <c r="J79" t="n">
         <v>-16</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>8.930000305175781</v>
+        <v>8.739999771118164</v>
       </c>
       <c r="I80" t="n">
-        <v>3.359462371195235</v>
+        <v>3.43249436906586</v>
       </c>
       <c r="J80" t="n">
         <v>-16</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2.220000028610229</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I81" t="n">
-        <v>4.864864802168965</v>
+        <v>4.954128288658833</v>
       </c>
       <c r="J81" t="n">
         <v>-16</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>89.30000305175781</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="I82" t="n">
-        <v>2.306830828220728</v>
+        <v>2.244008639998138</v>
       </c>
       <c r="J82" t="n">
         <v>-16</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>15.17000007629395</v>
+        <v>15.05000019073486</v>
       </c>
       <c r="I83" t="n">
-        <v>4.943968333737979</v>
+        <v>4.983388641162395</v>
       </c>
       <c r="J83" t="n">
         <v>-16</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>14.27000045776367</v>
+        <v>13.98999977111816</v>
       </c>
       <c r="I84" t="n">
-        <v>2.102312476358635</v>
+        <v>2.144388884261019</v>
       </c>
       <c r="J84" t="n">
         <v>-16</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>51.79999923706055</v>
+        <v>52</v>
       </c>
       <c r="I85" t="n">
-        <v>1.640926665095129</v>
+        <v>1.634615384615385</v>
       </c>
       <c r="J85" t="n">
         <v>-16</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>34.88000106811523</v>
+        <v>35.09999847412109</v>
       </c>
       <c r="I86" t="n">
-        <v>2.436926530879634</v>
+        <v>2.421652526927308</v>
       </c>
       <c r="J86" t="n">
         <v>-16</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>66.73999786376953</v>
+        <v>67.26000213623047</v>
       </c>
       <c r="I87" t="n">
-        <v>1.947857419254905</v>
+        <v>1.932798035550074</v>
       </c>
       <c r="J87" t="n">
         <v>-16</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>6.960000038146973</v>
+        <v>6.880000114440918</v>
       </c>
       <c r="I88" t="n">
-        <v>8.620689607923389</v>
+        <v>8.720930087495459</v>
       </c>
       <c r="J88" t="n">
         <v>-16</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.550000190734863</v>
+        <v>5.510000228881836</v>
       </c>
       <c r="I90" t="n">
-        <v>3.603603479759853</v>
+        <v>3.629763914557708</v>
       </c>
       <c r="J90" t="n">
         <v>-16</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>23.39999961853027</v>
+        <v>23.44000053405762</v>
       </c>
       <c r="I91" t="n">
-        <v>4.273504343171475</v>
+        <v>4.266211506894081</v>
       </c>
       <c r="J91" t="n">
         <v>-16</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>23.40999984741211</v>
+        <v>23.45499992370605</v>
       </c>
       <c r="I93" t="n">
-        <v>1.15335327535189</v>
+        <v>1.151140485518015</v>
       </c>
       <c r="J93" t="n">
         <v>-16</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>9.439999580383301</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I94" t="n">
-        <v>2.118644161972296</v>
+        <v>2.127659660812527</v>
       </c>
       <c r="J94" t="n">
         <v>-16</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>8.670000076293945</v>
+        <v>8.545000076293945</v>
       </c>
       <c r="I95" t="n">
-        <v>2.768166065606192</v>
+        <v>2.808660010031158</v>
       </c>
       <c r="J95" t="n">
         <v>-16</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>20.64999961853027</v>
+        <v>20.42000007629395</v>
       </c>
       <c r="I96" t="n">
-        <v>3.825665930236113</v>
+        <v>3.868756106994972</v>
       </c>
       <c r="J96" t="n">
         <v>-16</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>34.90000152587891</v>
+        <v>34.5</v>
       </c>
       <c r="I99" t="n">
-        <v>1.002865285666161</v>
+        <v>1.014492753623188</v>
       </c>
       <c r="J99" t="n">
         <v>-16</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.574999809265137</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="I100" t="n">
-        <v>8.430418495509464</v>
+        <v>8.580495305368434</v>
       </c>
       <c r="J100" t="n">
         <v>-16</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>13.19999980926514</v>
+        <v>12.89999961853027</v>
       </c>
       <c r="I102" t="n">
-        <v>1.515151537044865</v>
+        <v>1.550387642746198</v>
       </c>
       <c r="J102" t="n">
         <v>-16</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.409999847412109</v>
+        <v>7.355000019073486</v>
       </c>
       <c r="I103" t="n">
-        <v>1.390013523900031</v>
+        <v>1.400407882160345</v>
       </c>
       <c r="J103" t="n">
         <v>-16</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.710999965667725</v>
+        <v>5.64300012588501</v>
       </c>
       <c r="I104" t="n">
-        <v>3.326912994960689</v>
+        <v>3.367003291891681</v>
       </c>
       <c r="J104" t="n">
         <v>-16</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>9.895999908447266</v>
+        <v>9.880000114440918</v>
       </c>
       <c r="I105" t="n">
-        <v>4.365400202067939</v>
+        <v>4.372469584980827</v>
       </c>
       <c r="J105" t="n">
         <v>-16</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>26.31999969482422</v>
+        <v>26.11000061035156</v>
       </c>
       <c r="I106" t="n">
-        <v>1.671732542179798</v>
+        <v>1.685178053291801</v>
       </c>
       <c r="J106" t="n">
         <v>-16</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>7.050000190734863</v>
+        <v>6.980000019073486</v>
       </c>
       <c r="I108" t="n">
-        <v>6.666666486302734</v>
+        <v>6.733524336900889</v>
       </c>
       <c r="J108" t="n">
         <v>-16</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>54.47999954223633</v>
+        <v>53.88000106811523</v>
       </c>
       <c r="I109" t="n">
-        <v>2.569750388699309</v>
+        <v>2.598366689395786</v>
       </c>
       <c r="J109" t="n">
         <v>-16</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.45199990272522</v>
+        <v>3.381999969482422</v>
       </c>
       <c r="I110" t="n">
-        <v>8.690614381627347</v>
+        <v>8.870490913869277</v>
       </c>
       <c r="J110" t="n">
         <v>-16</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>15.55000019073486</v>
+        <v>15.80000019073486</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7717041705986566</v>
+        <v>0.7594936617175999</v>
       </c>
       <c r="J111" t="n">
         <v>-16</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3.400000095367432</v>
+        <v>3.369999885559082</v>
       </c>
       <c r="I112" t="n">
-        <v>4.999999859753782</v>
+        <v>5.044510557061846</v>
       </c>
       <c r="J112" t="n">
         <v>-16</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>22.54999923706055</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="I113" t="n">
-        <v>3.104212965335988</v>
+        <v>3.153153044789871</v>
       </c>
       <c r="J113" t="n">
         <v>-16</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.539999961853027</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="I115" t="n">
-        <v>5.956678741377123</v>
+        <v>6.04395600172919</v>
       </c>
       <c r="J115" t="n">
         <v>-16</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.8859999775886536</v>
+        <v>0.8679999709129333</v>
       </c>
       <c r="I116" t="n">
-        <v>7.90067740075036</v>
+        <v>8.064516399277796</v>
       </c>
       <c r="J116" t="n">
         <v>-16</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>50.84999847412109</v>
+        <v>50.59999847412109</v>
       </c>
       <c r="I117" t="n">
-        <v>1.396263562055637</v>
+        <v>1.403162097649317</v>
       </c>
       <c r="J117" t="n">
         <v>-16</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>107.3000030517578</v>
+        <v>104.5</v>
       </c>
       <c r="I118" t="n">
-        <v>1.25815467064694</v>
+        <v>1.291866028708134</v>
       </c>
       <c r="J118" t="n">
         <v>-16</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>8.199999809265137</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9756097787905852</v>
+        <v>0.9925557795914417</v>
       </c>
       <c r="J119" t="n">
         <v>-16</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.329999923706055</v>
+        <v>4.309000015258789</v>
       </c>
       <c r="I121" t="n">
-        <v>3.926097066867768</v>
+        <v>3.945230898073928</v>
       </c>
       <c r="J121" t="n">
         <v>-16</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>56.5</v>
+        <v>56.40000152587891</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7964601769911505</v>
+        <v>0.7978723188394231</v>
       </c>
       <c r="J123" t="n">
         <v>-16</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5.840000152587891</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6849314889533817</v>
+        <v>0.6896551497342619</v>
       </c>
       <c r="J124" t="n">
         <v>-16</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>38.88000106811523</v>
+        <v>38.81999969482422</v>
       </c>
       <c r="I125" t="n">
-        <v>2.700617209758992</v>
+        <v>2.704791365930882</v>
       </c>
       <c r="J125" t="n">
         <v>-16</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>17.32999992370605</v>
+        <v>17.51000022888184</v>
       </c>
       <c r="I127" t="n">
-        <v>2.192729380686207</v>
+        <v>2.170188435367406</v>
       </c>
       <c r="J127" t="n">
         <v>-16</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>27.36000061035156</v>
+        <v>27.69000053405762</v>
       </c>
       <c r="I128" t="n">
-        <v>2.192982407218924</v>
+        <v>2.166847195477745</v>
       </c>
       <c r="J128" t="n">
         <v>-16</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>37.90000152587891</v>
+        <v>36.04999923706055</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9234828124241966</v>
+        <v>0.9708738069547276</v>
       </c>
       <c r="J129" t="n">
         <v>-16</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2.950000047683716</v>
+        <v>2.900000095367432</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3389830453681453</v>
+        <v>0.3448275748671309</v>
       </c>
       <c r="J131" t="n">
         <v>-16</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>20.79999923706055</v>
+        <v>20.67000007629395</v>
       </c>
       <c r="I132" t="n">
-        <v>5.384615582121908</v>
+        <v>5.418480870179136</v>
       </c>
       <c r="J132" t="n">
         <v>-16</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.203999996185303</v>
+        <v>2.155999898910522</v>
       </c>
       <c r="I135" t="n">
-        <v>4.187840297629466</v>
+        <v>4.28107626751937</v>
       </c>
       <c r="J135" t="n">
         <v>-16</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>9.140000343322754</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I136" t="n">
-        <v>3.829321519180174</v>
+        <v>3.846153684924045</v>
       </c>
       <c r="J136" t="n">
         <v>-23</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>7.449999809265137</v>
+        <v>6.949999809265137</v>
       </c>
       <c r="I137" t="n">
-        <v>1.288590637017337</v>
+        <v>1.381295001936851</v>
       </c>
       <c r="J137" t="n">
         <v>-23</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>11.30000019073486</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="I139" t="n">
-        <v>1.769911474550104</v>
+        <v>1.724137874335655</v>
       </c>
       <c r="J139" t="n">
         <v>-23</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>9.020000457763672</v>
+        <v>9.079999923706055</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6651884363083036</v>
+        <v>0.6607929570941081</v>
       </c>
       <c r="J140" t="n">
         <v>-23</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>18.63999938964844</v>
+        <v>18.68000030517578</v>
       </c>
       <c r="I141" t="n">
-        <v>2.682403521309506</v>
+        <v>2.676659485179248</v>
       </c>
       <c r="J141" t="n">
         <v>-23</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>15.46000003814697</v>
+        <v>15.19999980926514</v>
       </c>
       <c r="I143" t="n">
-        <v>3.234152644025023</v>
+        <v>3.289473725487982</v>
       </c>
       <c r="J143" t="n">
         <v>-23</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>3.180000066757202</v>
+        <v>3.150000095367432</v>
       </c>
       <c r="I145" t="n">
-        <v>3.459119424238636</v>
+        <v>3.492063386339963</v>
       </c>
       <c r="J145" t="n">
         <v>-23</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>4.900000095367432</v>
+        <v>4.840000152587891</v>
       </c>
       <c r="I147" t="n">
-        <v>1.938775472470196</v>
+        <v>1.962809855474997</v>
       </c>
       <c r="J147" t="n">
         <v>-23</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1.379999995231628</v>
+        <v>1.330000042915344</v>
       </c>
       <c r="I148" t="n">
-        <v>2.173913050989873</v>
+        <v>2.255639024961259</v>
       </c>
       <c r="J148" t="n">
         <v>-23</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>8.399999618530273</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I149" t="n">
-        <v>1.071428620085427</v>
+        <v>1.097561001139408</v>
       </c>
       <c r="J149" t="n">
         <v>-23</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>7.130000114440918</v>
+        <v>7.079999923706055</v>
       </c>
       <c r="I151" t="n">
-        <v>3.085553947669898</v>
+        <v>3.107344666253049</v>
       </c>
       <c r="J151" t="n">
         <v>-23</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>25.10000038146973</v>
+        <v>25</v>
       </c>
       <c r="I152" t="n">
-        <v>2.430278847526781</v>
+        <v>2.44</v>
       </c>
       <c r="J152" t="n">
         <v>-30</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>2.799999952316284</v>
+        <v>2.839999914169312</v>
       </c>
       <c r="I153" t="n">
-        <v>5.357142948374458</v>
+        <v>5.281690300468702</v>
       </c>
       <c r="J153" t="n">
         <v>-30</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>11.05000019073486</v>
+        <v>10.80000019073486</v>
       </c>
       <c r="I154" t="n">
-        <v>6.334841519613111</v>
+        <v>6.481481367014401</v>
       </c>
       <c r="J154" t="n">
         <v>-30</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>9.390000343322754</v>
+        <v>9.329999923706055</v>
       </c>
       <c r="I155" t="n">
-        <v>5.436634519007419</v>
+        <v>5.471597043670924</v>
       </c>
       <c r="J155" t="n">
         <v>-30</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>7.099999904632568</v>
+        <v>7.105000019073486</v>
       </c>
       <c r="I156" t="n">
-        <v>3.802816952488012</v>
+        <v>3.800140735752015</v>
       </c>
       <c r="J156" t="n">
         <v>-30</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>7.409999847412109</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="I157" t="n">
-        <v>4.723346925873892</v>
+        <v>4.794520422673672</v>
       </c>
       <c r="J157" t="n">
         <v>-30</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>42.79999923706055</v>
+        <v>42.40000152587891</v>
       </c>
       <c r="I158" t="n">
-        <v>2.570093503757611</v>
+        <v>2.594339529277171</v>
       </c>
       <c r="J158" t="n">
         <v>-30</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>17</v>
+        <v>17.04999923706055</v>
       </c>
       <c r="I159" t="n">
-        <v>4.411764705882353</v>
+        <v>4.398827176307261</v>
       </c>
       <c r="J159" t="n">
         <v>-30</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>11.14999961853027</v>
+        <v>11.05000019073486</v>
       </c>
       <c r="I160" t="n">
-        <v>3.856502374093175</v>
+        <v>3.891402647762339</v>
       </c>
       <c r="J160" t="n">
         <v>-30</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>4.335000038146973</v>
+        <v>4.349999904632568</v>
       </c>
       <c r="I161" t="n">
-        <v>3.46020758200774</v>
+        <v>3.448275937667407</v>
       </c>
       <c r="J161" t="n">
         <v>-30</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>11.88000011444092</v>
+        <v>11.9399995803833</v>
       </c>
       <c r="I162" t="n">
-        <v>1.659671701183977</v>
+        <v>1.651331716325491</v>
       </c>
       <c r="J162" t="n">
         <v>-30</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>27.75</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="I163" t="n">
-        <v>3.963963963963964</v>
+        <v>4.029304141908979</v>
       </c>
       <c r="J163" t="n">
         <v>-30</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>69.69999694824219</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="I164" t="n">
-        <v>0.67431853741545</v>
+        <v>0.6676136218935007</v>
       </c>
       <c r="J164" t="n">
         <v>-30</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>93.80000305175781</v>
+        <v>91.69999694824219</v>
       </c>
       <c r="I165" t="n">
-        <v>1.279317655605889</v>
+        <v>1.308615092623515</v>
       </c>
       <c r="J165" t="n">
         <v>-30</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>22.14999961853027</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="I166" t="n">
-        <v>1.218961646275258</v>
+        <v>1.210762373261811</v>
       </c>
       <c r="J166" t="n">
         <v>-30</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>35.34999847412109</v>
+        <v>34.65000152587891</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8486563308330068</v>
+        <v>0.8658008276736733</v>
       </c>
       <c r="J168" t="n">
         <v>-30</v>
@@ -10296,44 +10296,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ESPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>